--- a/resultado_operadoras.xlsx
+++ b/resultado_operadoras.xlsx
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>82379476.41</v>
+        <v>82379476.40999998</v>
       </c>
       <c r="D1204" t="n">
         <v>68963001.41000003</v>
@@ -24294,7 +24294,7 @@
         </is>
       </c>
       <c r="C1326" t="n">
-        <v>271184138.2599999</v>
+        <v>271184138.26</v>
       </c>
       <c r="D1326" t="n">
         <v>203156493.91</v>

--- a/resultado_operadoras.xlsx
+++ b/resultado_operadoras.xlsx
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>82379476.40999998</v>
+        <v>82379476.41</v>
       </c>
       <c r="D1204" t="n">
         <v>68963001.41000003</v>

--- a/resultado_operadoras.xlsx
+++ b/resultado_operadoras.xlsx
@@ -22098,7 +22098,7 @@
         </is>
       </c>
       <c r="C1204" t="n">
-        <v>82379476.41</v>
+        <v>82379476.40999998</v>
       </c>
       <c r="D1204" t="n">
         <v>68963001.41000003</v>

--- a/resultado_operadoras.xlsx
+++ b/resultado_operadoras.xlsx
@@ -1146,7 +1146,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>65791157.76000001</v>
+        <v>65791157.76</v>
       </c>
       <c r="D40" t="n">
         <v>56491595.26</v>
